--- a/EUC/Creel_Data/2023_Creel/2023_Creel_Metadata.xlsx
+++ b/EUC/Creel_Data/2023_Creel/2023_Creel_Metadata.xlsx
@@ -1857,8 +1857,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE9114A9D0DECB469CD3434F7556ACE4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ecdf13fd03e578e190d1c2fef808890a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="62120a19-a38a-4c78-8e86-03b65bdcf4fa" xmlns:ns3="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d204db95074059abcc46212eb5d192a9" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE9114A9D0DECB469CD3434F7556ACE4" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d052d5d0cbba206a92698e59fff1adc9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="62120a19-a38a-4c78-8e86-03b65bdcf4fa" xmlns:ns3="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="107f69d6c17fede4ad775fb4a7f1d6c8" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="62120a19-a38a-4c78-8e86-03b65bdcf4fa"/>
     <xsd:import namespace="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d"/>
@@ -1870,21 +1870,20 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
                 <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1919,21 +1918,9 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
     <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
@@ -1946,38 +1933,45 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="360a6a1c-50a4-4ec0-87e3-f00760ffe76b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="360a6a1c-50a4-4ec0-87e3-f00760ffe76b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="24" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="15" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1996,14 +1990,14 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="16" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{2e22025f-5e6f-4000-be51-ea90689ba644}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d">
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c1f5b161-9dbc-4d55-8f07-a8caea185eb2}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -2114,6 +2108,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="62120a19-a38a-4c78-8e86-03b65bdcf4fa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF885F9F-9473-4277-AFC4-0BC2E0A6233F}">
   <ds:schemaRefs>
@@ -2123,21 +2130,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D822E1B3-9EA3-4448-8EAB-88F78930A708}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="62120a19-a38a-4c78-8e86-03b65bdcf4fa"/>
-    <ds:schemaRef ds:uri="671c5c8a-d1dd-40a7-bcfd-3ed591bedb5d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82432E1D-2193-432D-9996-14053E54D328}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A93D26FE-E00E-4891-A474-30A31D769BF8}"/>
 </file>